--- a/Tools/Luban/__define__.xlsx
+++ b/Tools/Luban/__define__.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Unity\MiniShip\Tools\Luban\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F8CDC6-8D22-4709-A75D-25DAA54A0E13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CBB30C4-FE21-430A-849E-A51F4A2429AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25490" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="156">
   <si>
     <t>##var</t>
   </si>
@@ -301,290 +301,295 @@
     <t>浮冰</t>
   </si>
   <si>
+    <t>Coastline</t>
+  </si>
+  <si>
+    <t>海岸线</t>
+  </si>
+  <si>
+    <t>Land</t>
+  </si>
+  <si>
+    <t>陆地</t>
+  </si>
+  <si>
+    <t>key_value@__table__.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cargo@__table__.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>event@__table__.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>port@__table__.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>port_upgrade@__table__.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>terrain@__table__.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>取值one|map|list，为空自动为map</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>list</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>None</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>键值表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>货物表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>事件表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>港口表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>港口容量上限提升表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>港口升级表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>地形表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ship@__table__.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Table.Ship</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Table._TbShip</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>key_value</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>cargo</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>event</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>port</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>port_upgrade</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ship</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>terrain</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Table._TbPortLimitTips</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Table.PortLimitTips</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>port_limit_tips@__table__.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>port_limit_tips</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bean.SpriteAsset</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>time</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>range</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>path</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>精灵图资源路径</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>资源路径</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>时间粒度</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>分钟</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>变化值</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>变化时间</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>max</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大值（不包含）</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>船只表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>upgrade_award</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>升级奖励表</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>upgrade_award@__table__.xlsx</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Table.UpgradeAward</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Table._TbUpgradeAward</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>货物类型</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bean.CargoType</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>cargo</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bean.ShipType</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ship</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>船只类型</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bean.ShipAward</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>船只奖励</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>type</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>num</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>奖励的数量</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>奖励的船只类型</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
     <t>DeepCanal</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>深水运河</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>潜在深水运河</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>浅水运河</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>潜在浅水运河</t>
+    <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
     <t>ShallowCanal</t>
-  </si>
-  <si>
-    <t>浅水运河</t>
-  </si>
-  <si>
-    <t>Coastline</t>
-  </si>
-  <si>
-    <t>海岸线</t>
-  </si>
-  <si>
-    <t>Land</t>
-  </si>
-  <si>
-    <t>陆地</t>
-  </si>
-  <si>
-    <t>key_value@__table__.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cargo@__table__.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>event@__table__.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>port@__table__.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>port_upgrade@__table__.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>terrain@__table__.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>取值one|map|list，为空自动为map</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>list</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>None</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>无</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>键值表</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>货物表</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>事件表</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>港口表</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>港口容量上限提升表</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>港口升级表</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>地形表</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ship@__table__.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Table.Ship</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Table._TbShip</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>key_value</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>cargo</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>event</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>port</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>port_upgrade</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ship</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>terrain</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Table._TbPortLimitTips</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Table.PortLimitTips</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>port_limit_tips@__table__.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>port_limit_tips</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bean.SpriteAsset</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bean.TextAsset</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>time</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>range</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>path</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>精灵图资源路径</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>多语言文本主键</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>key</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>主键</t>
-  </si>
-  <si>
-    <t>资源路径</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>时间粒度</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>分钟</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>变化值</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>变化时间</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>max</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>最大值（不包含）</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>船只表</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>upgrade_award</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>升级奖励表</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>upgrade_award@__table__.xlsx</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Table.UpgradeAward</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Table._TbUpgradeAward</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>货物类型</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bean.CargoType</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>cargo</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bean.ShipType</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>ship</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>船只类型</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bean.ShipAward</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>船只奖励</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>type</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>num</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>奖励的数量</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>奖励的船只类型</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>HiddenDeepCanal</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>HiddenShallowCanal</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -1138,7 +1143,7 @@
         <v>23</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>24</v>
@@ -1158,16 +1163,16 @@
         <v>1</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G4" t="s">
         <v>26</v>
       </c>
       <c r="I4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
@@ -1181,16 +1186,16 @@
         <v>1</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="G5" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I5" t="s">
         <v>97</v>
       </c>
-      <c r="I5" t="s">
-        <v>101</v>
-      </c>
       <c r="K5" s="2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -1204,13 +1209,13 @@
         <v>1</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="I6" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -1224,33 +1229,33 @@
         <v>1</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="I7" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="I8" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -1264,36 +1269,36 @@
         <v>1</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I9" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -1307,36 +1312,36 @@
         <v>1</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="I11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
@@ -1359,7 +1364,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F8920B7-A19D-41BF-861D-3CAD7B39D22F}">
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
@@ -1470,202 +1475,180 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D4" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="D4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="N4" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>131</v>
       </c>
       <c r="P4" s="2"/>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
-        <v>122</v>
+        <v>55</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="K5" s="2"/>
+        <v>119</v>
+      </c>
       <c r="L5" s="2" t="s">
-        <v>123</v>
+        <v>56</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="P5" s="2"/>
+        <v>125</v>
+      </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D6" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="L6" s="2" t="s">
+      <c r="N6" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="J7" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="L7" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="N6" s="2" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B7" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="N7" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="G8" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="J8" s="2" t="s">
-        <v>125</v>
+        <v>63</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>56</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>134</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B9" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D9" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="J9" s="2" t="s">
-        <v>63</v>
+        <v>128</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>56</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>64</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>136</v>
+      </c>
       <c r="J10" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B11" s="2" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="B12" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="N12" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D12" t="b">
-        <v>1</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>123</v>
-      </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B13" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="D13" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>151</v>
-      </c>
       <c r="J13" s="2" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>147</v>
+        <v>56</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="J14" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>
@@ -1680,16 +1663,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12FC7480-6B53-4E28-A47C-7D9E38433696}">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.9140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="5.25" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
@@ -1785,22 +1768,20 @@
       <c r="C4" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="D4" s="8" t="b">
-        <v>1</v>
-      </c>
+      <c r="D4" s="8"/>
       <c r="E4" s="9"/>
       <c r="F4" s="9" t="s">
         <v>75</v>
       </c>
       <c r="G4" s="9"/>
       <c r="H4" s="2" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
@@ -1865,14 +1846,14 @@
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
       <c r="H8" s="9" t="s">
-        <v>82</v>
+        <v>148</v>
       </c>
       <c r="I8" s="9"/>
       <c r="J8" s="9">
         <v>8</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>83</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
@@ -1883,14 +1864,14 @@
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
       <c r="H9" s="9" t="s">
-        <v>84</v>
+        <v>153</v>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="9">
         <v>16</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>85</v>
+        <v>151</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
@@ -1901,26 +1882,50 @@
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
       <c r="H10" s="9" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="I10" s="9"/>
       <c r="J10" s="9">
         <v>32</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="H11" s="9" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="I11" s="9"/>
       <c r="J11" s="9">
         <v>64</v>
       </c>
       <c r="K11" s="9" t="s">
-        <v>89</v>
+        <v>85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H12" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9">
+        <v>64</v>
+      </c>
+      <c r="K12" s="9" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="H13" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="I13" s="9"/>
+      <c r="J13" s="9">
+        <v>64</v>
+      </c>
+      <c r="K13" s="9" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>
